--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -756,31 +756,31 @@
     <t>NK1-3</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson</t>
-  </si>
-  <si>
-    <t>RolePerson</t>
-  </si>
-  <si>
-    <t>The nature of the relationship. Rôle de la personne</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person-role</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RolePerson.id</t>
+    <t>RelatedPerson.relationship:Role</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.id</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.id</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.extension</t>
+    <t>RelatedPerson.relationship:Role.extension</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.extension</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding</t>
+    <t>RelatedPerson.relationship:Role.coding</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding</t>
@@ -807,19 +807,19 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.id</t>
+    <t>RelatedPerson.relationship:Role.coding.id</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.id</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.extension</t>
+    <t>RelatedPerson.relationship:Role.coding.extension</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.extension</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.system</t>
+    <t>RelatedPerson.relationship:Role.coding.system</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.system</t>
@@ -849,7 +849,7 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.version</t>
+    <t>RelatedPerson.relationship:Role.coding.version</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.version</t>
@@ -873,7 +873,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.code</t>
+    <t>RelatedPerson.relationship:Role.coding.code</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.code</t>
@@ -900,7 +900,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.display</t>
+    <t>RelatedPerson.relationship:Role.coding.display</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.display</t>
@@ -924,7 +924,7 @@
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.userSelected</t>
+    <t>RelatedPerson.relationship:Role.coding.userSelected</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.userSelected</t>
@@ -951,7 +951,7 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.text</t>
+    <t>RelatedPerson.relationship:Role.text</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.text</t>
@@ -978,52 +978,52 @@
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RelatedPerson</t>
-  </si>
-  <si>
-    <t>sliceRelationship</t>
-  </si>
-  <si>
-    <t>The nature of the relationship. Relation de la personne</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.id</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.extension</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.id</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.extension</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.system</t>
+    <t>RelatedPerson.relationship:RelationType</t>
+  </si>
+  <si>
+    <t>RelationType</t>
+  </si>
+  <si>
+    <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.system</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R216-HL7RoleCode/FHIR/TRE-R216-HL7RoleCode</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.version</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.code</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.display</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.userSelected</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.text</t>
+    <t>RelatedPerson.relationship:RelationType.coding.version</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.code</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.display</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.userSelected</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.text</t>
   </si>
   <si>
     <t>RelatedPerson.name</t>
@@ -1601,11 +1601,11 @@
   <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.84375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.6171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.27734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.31640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.0859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="16.4921875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
@@ -1626,7 +1626,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.12109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>78</v>
@@ -5556,14 +5556,12 @@
         <v>226</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>312</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>77</v>
       </c>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -418,7 +418,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -438,7 +438,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1120,7 +1120,7 @@
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
